--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9861,0.0055,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.0089,0.0010,0.0001,0.9969</t>
-  </si>
-  <si>
-    <t>0.6096,0.0016,0.0006,0.6467</t>
-  </si>
-  <si>
-    <t>0.1155,0.0005,0.0007,0.9607</t>
-  </si>
-  <si>
-    <t>0.9966,0.0011,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0006,0.0005,0.0097</t>
-  </si>
-  <si>
-    <t>0.9899,0.0030,0.0041,0.0010</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9786,0.0109,0.0023,0.0060</t>
-  </si>
-  <si>
-    <t>0.9805,0.0151,0.0011,0.0022</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9893,0.0026,0.0026,0.0025</t>
-  </si>
-  <si>
-    <t>0.8606,0.0738,0.0504,0.0095</t>
-  </si>
-  <si>
-    <t>0.3554,0.0124,0.7251,0.0048</t>
-  </si>
-  <si>
-    <t>0.6288,0.0057,0.6009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0438,0.0039,0.9627,0.0015</t>
-  </si>
-  <si>
-    <t>0.8853,0.0032,0.1249,0.0043</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9985,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.0367,0.9700,0.0079,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.9946,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.9945,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.1202,0.0112,0.8835,0.0123</t>
-  </si>
-  <si>
-    <t>0.0235,0.0036,0.9662,0.0070</t>
-  </si>
-  <si>
-    <t>0.1019,0.0002,0.9430,0.0007</t>
-  </si>
-  <si>
-    <t>0.0032,0.0013,0.9907,0.0031</t>
-  </si>
-  <si>
-    <t>0.0378,0.0010,0.9609,0.0029</t>
-  </si>
-  <si>
-    <t>0.1217,0.0007,0.9221,0.0020</t>
-  </si>
-  <si>
-    <t>0.0049,0.0010,0.9903,0.0049</t>
-  </si>
-  <si>
-    <t>0.6763,0.4626,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.5122,0.3954,0.1077,0.0093</t>
-  </si>
-  <si>
-    <t>0.0094,0.0052,0.9866,0.0017</t>
-  </si>
-  <si>
-    <t>0.0347,0.9434,0.0116,0.0009</t>
-  </si>
-  <si>
-    <t>0.9570,0.0386,0.0084,0.0025</t>
-  </si>
-  <si>
-    <t>0.8936,0.0367,0.0640,0.0015</t>
-  </si>
-  <si>
-    <t>0.2142,0.7808,0.0011,0.0029</t>
-  </si>
-  <si>
-    <t>0.0026,0.9921,0.1358,0.0029</t>
-  </si>
-  <si>
-    <t>0.0281,0.0652,0.8629,0.0101</t>
-  </si>
-  <si>
-    <t>0.0352,0.0041,0.9769,0.0015</t>
-  </si>
-  <si>
-    <t>0.0313,0.0302,0.9714,0.0005</t>
-  </si>
-  <si>
-    <t>0.0453,0.0020,0.8998,0.0306</t>
-  </si>
-  <si>
-    <t>0.0079,0.3717,0.9813,0.0008</t>
-  </si>
-  <si>
-    <t>0.0034,0.9881,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.0030,0.0012,0.9926,0.0051</t>
-  </si>
-  <si>
-    <t>0.0155,0.7595,0.0043,0.7799</t>
-  </si>
-  <si>
-    <t>0.0001,0.9909,0.0009,0.0614</t>
-  </si>
-  <si>
-    <t>0.0003,0.9982,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9982,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.9936,0.0053</t>
-  </si>
-  <si>
-    <t>0.0013,0.0657,0.9944,0.0020</t>
-  </si>
-  <si>
-    <t>0.0075,0.0014,0.9851,0.0069</t>
-  </si>
-  <si>
-    <t>0.0208,0.0006,0.9810,0.0017</t>
-  </si>
-  <si>
-    <t>0.0046,0.0036,0.9857,0.0046</t>
-  </si>
-  <si>
-    <t>0.0023,0.0059,0.9901,0.0022</t>
-  </si>
-  <si>
-    <t>0.9783,0.0076,0.0065,0.0036</t>
-  </si>
-  <si>
-    <t>0.9636,0.0092,0.0181,0.0069</t>
-  </si>
-  <si>
-    <t>0.9854,0.0056,0.0021,0.0029</t>
-  </si>
-  <si>
-    <t>0.0012,0.1032,0.9916,0.0060</t>
-  </si>
-  <si>
-    <t>0.9783,0.0043,0.0018,0.0090</t>
-  </si>
-  <si>
-    <t>0.9946,0.0006,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9951,0.0018,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.9531,0.9299,0.0010</t>
-  </si>
-  <si>
-    <t>0.0767,0.0839,0.8777,0.0060</t>
-  </si>
-  <si>
-    <t>0.0130,0.0200,0.9781,0.0028</t>
-  </si>
-  <si>
-    <t>0.0002,0.9653,0.9928,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9956,0.0043</t>
-  </si>
-  <si>
-    <t>0.0053,0.9908,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9960,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9281,0.0090,0.1065,0.0019</t>
-  </si>
-  <si>
-    <t>0.7601,0.1812,0.0710,0.0011</t>
-  </si>
-  <si>
-    <t>0.0020,0.0076,0.9951,0.0014</t>
-  </si>
-  <si>
-    <t>0.0037,0.8620,0.9677,0.0009</t>
-  </si>
-  <si>
-    <t>0.0084,0.8353,0.8533,0.0027</t>
-  </si>
-  <si>
-    <t>0.0002,0.9976,0.6582,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9542,0.9062,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.0006,0.9990</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.0038,0.9982</t>
-  </si>
-  <si>
-    <t>0.0035,0.0013,0.0027,0.9954</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.0011,0.9984</t>
-  </si>
-  <si>
-    <t>0.0048,0.0001,0.0009,0.9964</t>
-  </si>
-  <si>
-    <t>0.0009,0.9786,0.6381,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9000,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.0200,0.5494,0.7274,0.0002</t>
-  </si>
-  <si>
-    <t>0.0071,0.3393,0.9523,0.0035</t>
-  </si>
-  <si>
-    <t>0.0004,0.9900,0.9365,0.0001</t>
-  </si>
-  <si>
-    <t>0.0133,0.9442,0.1871,0.0013</t>
-  </si>
-  <si>
-    <t>0.9938,0.0025,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9648,0.0351,0.0045,0.0022</t>
-  </si>
-  <si>
-    <t>0.9756,0.0206,0.0039,0.0018</t>
-  </si>
-  <si>
-    <t>0.9817,0.0037,0.0011,0.0071</t>
-  </si>
-  <si>
-    <t>0.9923,0.0026,0.0007,0.0018</t>
-  </si>
-  <si>
-    <t>0.9669,0.0258,0.0065,0.0023</t>
-  </si>
-  <si>
-    <t>0.9692,0.0306,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9303,0.0723,0.0046,0.0042</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9962,0.0005,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.0036,0.0014,0.9913,0.0017</t>
-  </si>
-  <si>
-    <t>0.0303,0.0116,0.9758,0.0011</t>
-  </si>
-  <si>
-    <t>0.9789,0.0014,0.0099,0.0021</t>
-  </si>
-  <si>
-    <t>0.0656,0.0018,0.9679,0.0003</t>
-  </si>
-  <si>
-    <t>0.0028,0.9953,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.9980,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.9888,0.0021,0.0049</t>
-  </si>
-  <si>
-    <t>0.0019,0.9924,0.0011,0.0031</t>
-  </si>
-  <si>
-    <t>0.0038,0.9947,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.9976,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.2335,0.6774,0.0786,0.0046</t>
-  </si>
-  <si>
-    <t>0.9017,0.0080,0.0719,0.0141</t>
-  </si>
-  <si>
-    <t>0.8879,0.0021,0.1793,0.0027</t>
-  </si>
-  <si>
-    <t>0.2191,0.1127,0.4787,0.1671</t>
-  </si>
-  <si>
-    <t>0.1945,0.0256,0.7956,0.0109</t>
-  </si>
-  <si>
-    <t>0.0030,0.0553,0.1235,0.9465</t>
-  </si>
-  <si>
-    <t>0.0003,0.9952,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.9945,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0002,0.0038</t>
-  </si>
-  <si>
-    <t>0.0002,0.7939,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.9960,0.0211,0.0002</t>
-  </si>
-  <si>
-    <t>0.9100,0.1437,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.6066,0.5075,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0025,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9744,0.0062,0.0037,0.0100</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.9887,0.0030,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.9897,0.0019,0.0008,0.0046</t>
-  </si>
-  <si>
-    <t>0.9925,0.0024,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9845,0.0040,0.0029,0.0053</t>
-  </si>
-  <si>
-    <t>0.9877,0.0025,0.0087,0.0006</t>
-  </si>
-  <si>
-    <t>0.0113,0.8413,0.4867,0.0025</t>
-  </si>
-  <si>
-    <t>0.0027,0.7275,0.9561,0.0008</t>
-  </si>
-  <si>
-    <t>0.0038,0.0046,0.9933,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.5257,0.9772,0.0009</t>
-  </si>
-  <si>
-    <t>0.9159,0.0203,0.0513,0.0082</t>
-  </si>
-  <si>
-    <t>0.0959,0.0121,0.8945,0.0101</t>
-  </si>
-  <si>
-    <t>0.2470,0.0033,0.8357,0.0048</t>
-  </si>
-  <si>
-    <t>0.7593,0.0258,0.1972,0.0249</t>
-  </si>
-  <si>
-    <t>0.6171,0.0001,0.0001,0.7427</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0028,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0879,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0026,0.0010,0.0003,0.9980</t>
-  </si>
-  <si>
-    <t>0.0081,0.8639,0.4053,0.0098</t>
-  </si>
-  <si>
-    <t>0.9924,0.0025,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.0230,0.9622,0.0051,0.0170</t>
-  </si>
-  <si>
-    <t>0.9924,0.0009,0.0015,0.0023</t>
-  </si>
-  <si>
-    <t>0.0762,0.9130,0.0172,0.0084</t>
-  </si>
-  <si>
-    <t>0.9863,0.0005,0.0029,0.0049</t>
-  </si>
-  <si>
-    <t>0.1409,0.0018,0.0063,0.9395</t>
-  </si>
-  <si>
-    <t>0.9905,0.0023,0.0013,0.0026</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9706,0.3255</t>
-  </si>
-  <si>
-    <t>0.9176,0.0004,0.0023,0.0779</t>
-  </si>
-  <si>
-    <t>0.9500,0.0094,0.0106,0.0199</t>
-  </si>
-  <si>
-    <t>0.8604,0.1004,0.0398,0.0026</t>
-  </si>
-  <si>
-    <t>0.9571,0.0229,0.0089,0.0024</t>
-  </si>
-  <si>
-    <t>0.9469,0.0202,0.0185,0.0032</t>
-  </si>
-  <si>
-    <t>0.3202,0.5756,0.1520,0.0544</t>
-  </si>
-  <si>
-    <t>0.8466,0.0580,0.0942,0.0029</t>
-  </si>
-  <si>
-    <t>0.9543,0.0286,0.0070,0.0022</t>
-  </si>
-  <si>
-    <t>0.9828,0.0027,0.0033,0.0075</t>
-  </si>
-  <si>
-    <t>0.9638,0.0060,0.0028,0.0218</t>
-  </si>
-  <si>
-    <t>0.9836,0.0025,0.0075,0.0028</t>
-  </si>
-  <si>
-    <t>0.9944,0.0005,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9881,0.0045,0.0019,0.0025</t>
-  </si>
-  <si>
-    <t>0.9884,0.0064,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9856,0.0023,0.0060,0.0022</t>
-  </si>
-  <si>
-    <t>0.9801,0.0044,0.0043,0.0058</t>
-  </si>
-  <si>
-    <t>0.9806,0.0096,0.0009,0.0030</t>
-  </si>
-  <si>
-    <t>0.4220,0.6744,0.0052,0.0019</t>
-  </si>
-  <si>
-    <t>0.5519,0.4468,0.0306,0.0073</t>
-  </si>
-  <si>
-    <t>0.9531,0.0245,0.0274,0.0034</t>
-  </si>
-  <si>
-    <t>0.9473,0.0509,0.0110,0.0020</t>
-  </si>
-  <si>
-    <t>0.9716,0.0155,0.0105,0.0022</t>
-  </si>
-  <si>
-    <t>0.9887,0.0044,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.8573,0.1176,0.0067,0.0113</t>
-  </si>
-  <si>
-    <t>0.0097,0.0157,0.9907,0.0014</t>
-  </si>
-  <si>
-    <t>0.8583,0.0671,0.0803,0.0074</t>
-  </si>
-  <si>
-    <t>0.0065,0.0008,0.9890,0.0019</t>
-  </si>
-  <si>
-    <t>0.0029,0.4033,0.9915,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.0032,0.9868,0.0121</t>
-  </si>
-  <si>
-    <t>0.0021,0.0118,0.9935,0.0006</t>
-  </si>
-  <si>
-    <t>0.0355,0.0070,0.9792,0.0005</t>
-  </si>
-  <si>
-    <t>0.0064,0.0003,0.9941,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0093,0.9926,0.0024</t>
-  </si>
-  <si>
-    <t>0.0975,0.0175,0.8852,0.0124</t>
-  </si>
-  <si>
-    <t>0.3868,0.0024,0.7372,0.0051</t>
-  </si>
-  <si>
-    <t>0.7219,0.0322,0.2751,0.0163</t>
-  </si>
-  <si>
-    <t>0.1056,0.0185,0.9049,0.0040</t>
-  </si>
-  <si>
-    <t>0.6660,0.0130,0.4425,0.0013</t>
-  </si>
-  <si>
-    <t>0.5990,0.0503,0.4270,0.0201</t>
-  </si>
-  <si>
-    <t>0.7956,0.0233,0.0800,0.0483</t>
-  </si>
-  <si>
-    <t>0.5003,0.1004,0.3853,0.0032</t>
-  </si>
-  <si>
-    <t>0.0246,0.9679,0.0052,0.0037</t>
-  </si>
-  <si>
-    <t>0.0504,0.9481,0.0119,0.0019</t>
-  </si>
-  <si>
-    <t>0.3932,0.7393,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9625,0.0176,0.0007,0.0058</t>
-  </si>
-  <si>
-    <t>0.7082,0.2433,0.0094,0.0258</t>
-  </si>
-  <si>
-    <t>0.9718,0.0073,0.0123,0.0007</t>
-  </si>
-  <si>
-    <t>0.9753,0.0007,0.0262,0.0012</t>
-  </si>
-  <si>
-    <t>0.5961,0.0014,0.0045,0.5036</t>
-  </si>
-  <si>
-    <t>0.7338,0.0095,0.3544,0.0030</t>
-  </si>
-  <si>
-    <t>0.5781,0.0030,0.4615,0.0091</t>
-  </si>
-  <si>
-    <t>0.0115,0.0061,0.9736,0.0140</t>
-  </si>
-  <si>
-    <t>0.0146,0.0348,0.9477,0.0233</t>
-  </si>
-  <si>
-    <t>0.0702,0.0081,0.9539,0.0020</t>
-  </si>
-  <si>
-    <t>0.1225,0.0219,0.8568,0.0030</t>
-  </si>
-  <si>
-    <t>0.0102,0.7137,0.8800,0.0015</t>
-  </si>
-  <si>
-    <t>0.9926,0.0012,0.0002,0.0031</t>
-  </si>
-  <si>
-    <t>0.9890,0.0057,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.9763,0.0090,0.0018,0.0067</t>
-  </si>
-  <si>
-    <t>0.9833,0.0128,0.0026,0.0020</t>
-  </si>
-  <si>
-    <t>0.9840,0.0079,0.0011,0.0024</t>
-  </si>
-  <si>
-    <t>0.9811,0.0126,0.0039,0.0019</t>
-  </si>
-  <si>
-    <t>0.9835,0.0075,0.0034,0.0029</t>
-  </si>
-  <si>
-    <t>0.9964,0.0006,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0015,0.0147,0.9938,0.0040</t>
-  </si>
-  <si>
-    <t>0.0641,0.0451,0.8804,0.0497</t>
-  </si>
-  <si>
-    <t>0.9289,0.0013,0.0585,0.0045</t>
-  </si>
-  <si>
-    <t>0.0007,0.0016,0.9971,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0020,0.9928,0.0149</t>
-  </si>
-  <si>
-    <t>0.0049,0.0966,0.9416,0.0052</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9989,0.0019</t>
-  </si>
-  <si>
-    <t>0.0191,0.0143,0.9653,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9976,0.0011</t>
-  </si>
-  <si>
-    <t>0.0032,0.0033,0.9888,0.0057</t>
-  </si>
-  <si>
-    <t>0.0094,0.0176,0.9801,0.0018</t>
-  </si>
-  <si>
-    <t>0.8921,0.0033,0.1104,0.0069</t>
-  </si>
-  <si>
-    <t>0.7967,0.0019,0.1895,0.0143</t>
-  </si>
-  <si>
-    <t>0.9034,0.0095,0.0734,0.0080</t>
-  </si>
-  <si>
-    <t>0.9923,0.0029,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9863,0.0057,0.0036,0.0026</t>
-  </si>
-  <si>
-    <t>0.9933,0.0024,0.0006,0.0017</t>
-  </si>
-  <si>
-    <t>0.9895,0.0063,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9918,0.0061,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9679,0.0257,0.0020,0.0033</t>
-  </si>
-  <si>
-    <t>0.9874,0.0024,0.0013,0.0051</t>
-  </si>
-  <si>
-    <t>0.0214,0.0449,0.8878,0.0341</t>
-  </si>
-  <si>
-    <t>0.0049,0.0036,0.9925,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9973,0.0032</t>
-  </si>
-  <si>
-    <t>0.0055,0.0254,0.9678,0.0136</t>
-  </si>
-  <si>
-    <t>0.0003,0.0020,0.9983,0.0009</t>
-  </si>
-  <si>
-    <t>0.0891,0.0017,0.5700,0.1591</t>
-  </si>
-  <si>
-    <t>0.2586,0.0189,0.7912,0.0155</t>
-  </si>
-  <si>
-    <t>0.0081,0.0116,0.9721,0.0137</t>
-  </si>
-  <si>
-    <t>0.9450,0.0005,0.0017,0.0739</t>
-  </si>
-  <si>
-    <t>0.0266,0.0263,0.0030,0.9829</t>
-  </si>
-  <si>
-    <t>0.0988,0.0006,0.0016,0.9574</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0012,0.9990</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.9181,0.0052,0.0040,0.0749</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9819,0.0029,0.0058,0.0022</t>
+  </si>
+  <si>
+    <t>0.0041,0.0009,0.0006,0.9973</t>
+  </si>
+  <si>
+    <t>0.7910,0.0045,0.0020,0.2643</t>
+  </si>
+  <si>
+    <t>0.2010,0.0005,0.0033,0.8801</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9872,0.0023,0.0012,0.0080</t>
+  </si>
+  <si>
+    <t>0.9934,0.0038,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0005,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9940,0.0030,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9874,0.0064,0.0016,0.0019</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0021,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.6783,0.1377,0.1442,0.0092</t>
+  </si>
+  <si>
+    <t>0.8486,0.0010,0.2883,0.0008</t>
+  </si>
+  <si>
+    <t>0.2228,0.0075,0.8592,0.0009</t>
+  </si>
+  <si>
+    <t>0.0175,0.0153,0.9797,0.0004</t>
+  </si>
+  <si>
+    <t>0.9512,0.0026,0.0558,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.9981,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0525,0.9642,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.0042,0.9911,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.9978,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.3798,0.0071,0.7519,0.0022</t>
+  </si>
+  <si>
+    <t>0.0433,0.0070,0.9583,0.0033</t>
+  </si>
+  <si>
+    <t>0.0049,0.0020,0.9896,0.0044</t>
+  </si>
+  <si>
+    <t>0.0092,0.0035,0.9805,0.0043</t>
+  </si>
+  <si>
+    <t>0.0146,0.0032,0.9788,0.0044</t>
+  </si>
+  <si>
+    <t>0.0019,0.0005,0.9902,0.0168</t>
+  </si>
+  <si>
+    <t>0.0029,0.0005,0.9949,0.0016</t>
+  </si>
+  <si>
+    <t>0.4872,0.5945,0.0118,0.0011</t>
+  </si>
+  <si>
+    <t>0.9103,0.0652,0.0321,0.0029</t>
+  </si>
+  <si>
+    <t>0.0078,0.0162,0.9783,0.0106</t>
+  </si>
+  <si>
+    <t>0.0201,0.9712,0.0245,0.0003</t>
+  </si>
+  <si>
+    <t>0.9592,0.0296,0.0037,0.0029</t>
+  </si>
+  <si>
+    <t>0.9610,0.0545,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.8467,0.2011,0.0037,0.0020</t>
+  </si>
+  <si>
+    <t>0.0049,0.9924,0.0200,0.0016</t>
+  </si>
+  <si>
+    <t>0.0102,0.3691,0.3629,0.0266</t>
+  </si>
+  <si>
+    <t>0.0314,0.0680,0.9539,0.0102</t>
+  </si>
+  <si>
+    <t>0.0039,0.0056,0.9866,0.0044</t>
+  </si>
+  <si>
+    <t>0.0727,0.0008,0.8846,0.0119</t>
+  </si>
+  <si>
+    <t>0.0108,0.0651,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.0078,0.9865,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.0452,0.0121,0.9609,0.0031</t>
+  </si>
+  <si>
+    <t>0.0671,0.1987,0.0126,0.8511</t>
+  </si>
+  <si>
+    <t>0.0011,0.9865,0.0081,0.0185</t>
+  </si>
+  <si>
+    <t>0.0008,0.9967,0.0154,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9971,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.0135,0.9903,0.0024</t>
+  </si>
+  <si>
+    <t>0.0005,0.3184,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0093,0.0019,0.9848,0.0019</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9963,0.0056</t>
+  </si>
+  <si>
+    <t>0.0015,0.0041,0.9959,0.0017</t>
+  </si>
+  <si>
+    <t>0.0038,0.0062,0.9891,0.0018</t>
+  </si>
+  <si>
+    <t>0.9895,0.0083,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9671,0.0025,0.0410,0.0009</t>
+  </si>
+  <si>
+    <t>0.9630,0.0073,0.0182,0.0065</t>
+  </si>
+  <si>
+    <t>0.0028,0.0689,0.9879,0.0150</t>
+  </si>
+  <si>
+    <t>0.9931,0.0015,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9907,0.0026,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9951,0.0022,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.9485,0.9805,0.0003</t>
+  </si>
+  <si>
+    <t>0.0047,0.0258,0.9861,0.0019</t>
+  </si>
+  <si>
+    <t>0.0038,0.0070,0.9920,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.9548,0.9606,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0020,0.9904,0.0093</t>
+  </si>
+  <si>
+    <t>0.0056,0.9910,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.9948,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.8939,0.0071,0.1579,0.0008</t>
+  </si>
+  <si>
+    <t>0.5340,0.4813,0.0261,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0178,0.9962,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.9896,0.9900,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9405,0.8299,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.9953,0.5301,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9933,0.8985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0655,0.0020,0.0072,0.9453</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0006,0.0039,0.0017,0.9986</t>
+  </si>
+  <si>
+    <t>0.0047,0.0032,0.0152,0.9896</t>
+  </si>
+  <si>
+    <t>0.0013,0.0007,0.0019,0.9980</t>
+  </si>
+  <si>
+    <t>0.0017,0.0023,0.0005,0.9981</t>
+  </si>
+  <si>
+    <t>0.0014,0.9881,0.5425,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.8434,0.9748,0.0006</t>
+  </si>
+  <si>
+    <t>0.0147,0.8743,0.5217,0.0009</t>
+  </si>
+  <si>
+    <t>0.0214,0.3268,0.9159,0.0064</t>
+  </si>
+  <si>
+    <t>0.0002,0.9971,0.7561,0.0001</t>
+  </si>
+  <si>
+    <t>0.0240,0.9014,0.0656,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9747,0.0257,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.8935,0.1529,0.0019,0.0014</t>
+  </si>
+  <si>
+    <t>0.9793,0.0040,0.0004,0.0079</t>
+  </si>
+  <si>
+    <t>0.9902,0.0017,0.0008,0.0038</t>
+  </si>
+  <si>
+    <t>0.9935,0.0006,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.9532,0.0432,0.0056,0.0032</t>
+  </si>
+  <si>
+    <t>0.9753,0.0201,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0021,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9966,0.0005,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9922,0.0017,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.9869,0.0078,0.0012,0.0020</t>
+  </si>
+  <si>
+    <t>0.9938,0.0025,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9942,0.0023</t>
+  </si>
+  <si>
+    <t>0.0044,0.0013,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.9795,0.0012,0.0098,0.0022</t>
+  </si>
+  <si>
+    <t>0.0041,0.0014,0.9934,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.9977,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0127,0.9723,0.0065,0.0040</t>
+  </si>
+  <si>
+    <t>0.0056,0.9842,0.0065,0.0011</t>
+  </si>
+  <si>
+    <t>0.0079,0.9845,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.9974,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0566,0.8669,0.0539,0.0030</t>
+  </si>
+  <si>
+    <t>0.8647,0.0389,0.0839,0.0102</t>
+  </si>
+  <si>
+    <t>0.0692,0.0136,0.8785,0.0370</t>
+  </si>
+  <si>
+    <t>0.6507,0.1888,0.0625,0.0045</t>
+  </si>
+  <si>
+    <t>0.1846,0.0148,0.8195,0.0287</t>
+  </si>
+  <si>
+    <t>0.0233,0.0481,0.7398,0.4855</t>
+  </si>
+  <si>
+    <t>0.0010,0.9973,0.0080,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9919,0.0017,0.0050</t>
+  </si>
+  <si>
+    <t>0.0012,0.9947,0.0011,0.0031</t>
+  </si>
+  <si>
+    <t>0.0002,0.9436,0.9873,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.9863,0.0854,0.0005</t>
+  </si>
+  <si>
+    <t>0.9345,0.0925,0.0069,0.0011</t>
+  </si>
+  <si>
+    <t>0.3021,0.7857,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9956,0.0017,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0010,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.9903,0.0024,0.0008,0.0035</t>
+  </si>
+  <si>
+    <t>0.9783,0.0028,0.0085,0.0061</t>
+  </si>
+  <si>
+    <t>0.9936,0.0008,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.9932,0.0015,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9756,0.0020,0.0029,0.0168</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.1445,0.9816,0.0008</t>
+  </si>
+  <si>
+    <t>0.0059,0.8935,0.8541,0.0009</t>
+  </si>
+  <si>
+    <t>0.0353,0.0165,0.9725,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0073,0.9940,0.0008</t>
+  </si>
+  <si>
+    <t>0.9824,0.0042,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.8493,0.0083,0.1375,0.0103</t>
+  </si>
+  <si>
+    <t>0.6612,0.0017,0.5622,0.0014</t>
+  </si>
+  <si>
+    <t>0.7977,0.0101,0.2437,0.0103</t>
+  </si>
+  <si>
+    <t>0.0104,0.0014,0.0006,0.9937</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0004,0.0134,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0013,0.0019,0.0010,0.9983</t>
+  </si>
+  <si>
+    <t>0.0021,0.7776,0.9333,0.0042</t>
+  </si>
+  <si>
+    <t>0.9911,0.0057,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.0232,0.9721,0.0044,0.0092</t>
+  </si>
+  <si>
+    <t>0.9959,0.0006,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.3634,0.6832,0.0173,0.0093</t>
+  </si>
+  <si>
+    <t>0.9868,0.0012,0.0035,0.0039</t>
+  </si>
+  <si>
+    <t>0.7031,0.0018,0.0072,0.4167</t>
+  </si>
+  <si>
+    <t>0.9831,0.0037,0.0022,0.0056</t>
+  </si>
+  <si>
+    <t>0.0004,0.0030,0.9759,0.2951</t>
+  </si>
+  <si>
+    <t>0.9445,0.0004,0.0005,0.0855</t>
+  </si>
+  <si>
+    <t>0.8623,0.0047,0.0030,0.1678</t>
+  </si>
+  <si>
+    <t>0.8702,0.1378,0.0220,0.0034</t>
+  </si>
+  <si>
+    <t>0.9808,0.0030,0.0102,0.0011</t>
+  </si>
+  <si>
+    <t>0.9783,0.0116,0.0064,0.0007</t>
+  </si>
+  <si>
+    <t>0.0621,0.9284,0.0056,0.0028</t>
+  </si>
+  <si>
+    <t>0.8447,0.1297,0.0400,0.0072</t>
+  </si>
+  <si>
+    <t>0.8164,0.1737,0.0140,0.0069</t>
+  </si>
+  <si>
+    <t>0.9910,0.0011,0.0023,0.0027</t>
+  </si>
+  <si>
+    <t>0.9634,0.0047,0.0007,0.0255</t>
+  </si>
+  <si>
+    <t>0.9858,0.0048,0.0030,0.0026</t>
+  </si>
+  <si>
+    <t>0.9833,0.0018,0.0018,0.0098</t>
+  </si>
+  <si>
+    <t>0.9857,0.0040,0.0027,0.0035</t>
+  </si>
+  <si>
+    <t>0.9759,0.0117,0.0040,0.0054</t>
+  </si>
+  <si>
+    <t>0.9924,0.0006,0.0009,0.0037</t>
+  </si>
+  <si>
+    <t>0.9846,0.0001,0.0002,0.0268</t>
+  </si>
+  <si>
+    <t>0.9507,0.0436,0.0009,0.0041</t>
+  </si>
+  <si>
+    <t>0.7013,0.3706,0.0151,0.0036</t>
+  </si>
+  <si>
+    <t>0.6796,0.3885,0.0057,0.0041</t>
+  </si>
+  <si>
+    <t>0.7607,0.0343,0.3073,0.0049</t>
+  </si>
+  <si>
+    <t>0.6170,0.4035,0.0078,0.0058</t>
+  </si>
+  <si>
+    <t>0.9577,0.0175,0.0080,0.0095</t>
+  </si>
+  <si>
+    <t>0.9802,0.0082,0.0065,0.0024</t>
+  </si>
+  <si>
+    <t>0.3161,0.7689,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.0301,0.9956,0.0003</t>
+  </si>
+  <si>
+    <t>0.8177,0.1937,0.0277,0.0042</t>
+  </si>
+  <si>
+    <t>0.0038,0.0038,0.9946,0.0008</t>
+  </si>
+  <si>
+    <t>0.0112,0.0871,0.9776,0.0044</t>
+  </si>
+  <si>
+    <t>0.0092,0.0154,0.9867,0.0033</t>
+  </si>
+  <si>
+    <t>0.0144,0.0142,0.9685,0.0028</t>
+  </si>
+  <si>
+    <t>0.0171,0.0014,0.9882,0.0004</t>
+  </si>
+  <si>
+    <t>0.0067,0.0010,0.9920,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0220,0.9950,0.0011</t>
+  </si>
+  <si>
+    <t>0.2354,0.0130,0.8205,0.0042</t>
+  </si>
+  <si>
+    <t>0.0655,0.0012,0.9559,0.0007</t>
+  </si>
+  <si>
+    <t>0.6636,0.1149,0.2723,0.0089</t>
+  </si>
+  <si>
+    <t>0.0437,0.0842,0.9196,0.0058</t>
+  </si>
+  <si>
+    <t>0.4821,0.1337,0.1620,0.0007</t>
+  </si>
+  <si>
+    <t>0.8046,0.0207,0.1556,0.0007</t>
+  </si>
+  <si>
+    <t>0.7279,0.0176,0.2481,0.0225</t>
+  </si>
+  <si>
+    <t>0.0949,0.0082,0.9176,0.0030</t>
+  </si>
+  <si>
+    <t>0.1111,0.8929,0.0057,0.0041</t>
+  </si>
+  <si>
+    <t>0.0596,0.9458,0.0109,0.0012</t>
+  </si>
+  <si>
+    <t>0.4067,0.7499,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9364,0.0643,0.0037,0.0044</t>
+  </si>
+  <si>
+    <t>0.4096,0.6424,0.0233,0.0113</t>
+  </si>
+  <si>
+    <t>0.5841,0.1877,0.1737,0.0097</t>
+  </si>
+  <si>
+    <t>0.9686,0.0016,0.0211,0.0047</t>
+  </si>
+  <si>
+    <t>0.7810,0.0042,0.0139,0.2021</t>
+  </si>
+  <si>
+    <t>0.6641,0.0025,0.5275,0.0014</t>
+  </si>
+  <si>
+    <t>0.6758,0.0087,0.2353,0.0274</t>
+  </si>
+  <si>
+    <t>0.0041,0.0027,0.9871,0.0121</t>
+  </si>
+  <si>
+    <t>0.0722,0.0804,0.8082,0.0133</t>
+  </si>
+  <si>
+    <t>0.0527,0.0242,0.9531,0.0020</t>
+  </si>
+  <si>
+    <t>0.1499,0.0075,0.9083,0.0018</t>
+  </si>
+  <si>
+    <t>0.0126,0.0234,0.9565,0.0054</t>
+  </si>
+  <si>
+    <t>0.9923,0.0018,0.0005,0.0027</t>
+  </si>
+  <si>
+    <t>0.9903,0.0035,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.9792,0.0124,0.0013,0.0032</t>
+  </si>
+  <si>
+    <t>0.9884,0.0076,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.9893,0.0059,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9122,0.0528,0.0020,0.0114</t>
+  </si>
+  <si>
+    <t>0.9927,0.0006,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.9945,0.0003,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.0134,0.0445,0.9668,0.0064</t>
+  </si>
+  <si>
+    <t>0.0454,0.3703,0.8689,0.0133</t>
+  </si>
+  <si>
+    <t>0.7536,0.0044,0.1048,0.0497</t>
+  </si>
+  <si>
+    <t>0.0193,0.0075,0.9843,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9964,0.0039</t>
+  </si>
+  <si>
+    <t>0.0044,0.0286,0.9866,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9990,0.0007</t>
+  </si>
+  <si>
+    <t>0.0163,0.0186,0.9612,0.0051</t>
+  </si>
+  <si>
+    <t>0.0012,0.0054,0.9965,0.0004</t>
+  </si>
+  <si>
+    <t>0.0145,0.0035,0.9789,0.0019</t>
+  </si>
+  <si>
+    <t>0.1313,0.0495,0.8085,0.0093</t>
+  </si>
+  <si>
+    <t>0.4358,0.0016,0.7509,0.0010</t>
+  </si>
+  <si>
+    <t>0.6909,0.0040,0.2645,0.0274</t>
+  </si>
+  <si>
+    <t>0.9284,0.0048,0.0570,0.0087</t>
+  </si>
+  <si>
+    <t>0.9858,0.0057,0.0004,0.0023</t>
+  </si>
+  <si>
+    <t>0.9810,0.0060,0.0019,0.0056</t>
+  </si>
+  <si>
+    <t>0.9892,0.0071,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9830,0.0124,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9963,0.0006,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9757,0.0228,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9699,0.0117,0.0013,0.0072</t>
+  </si>
+  <si>
+    <t>0.9900,0.0034,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0310,0.0052,0.9657,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0203,0.9957,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.0078,0.9896,0.0031</t>
+  </si>
+  <si>
+    <t>0.0120,0.0296,0.9615,0.0110</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9965,0.0012</t>
+  </si>
+  <si>
+    <t>0.5829,0.0032,0.2875,0.0257</t>
+  </si>
+  <si>
+    <t>0.1956,0.0050,0.8608,0.0034</t>
+  </si>
+  <si>
+    <t>0.0157,0.0030,0.9813,0.0032</t>
+  </si>
+  <si>
+    <t>0.7730,0.0003,0.0006,0.4601</t>
+  </si>
+  <si>
+    <t>0.0066,0.0580,0.0023,0.9923</t>
+  </si>
+  <si>
+    <t>0.0244,0.0040,0.0032,0.9857</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.9857,0.0020,0.0018,0.0054</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3877,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
